--- a/Mallavarapu__2001/Mallavarapu__2001_registry_rows.xlsx
+++ b/Mallavarapu__2001/Mallavarapu__2001_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R1b8d36dde8b6430e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R6bae344f7200472d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R9d05aa27cd2f4f9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Re7f1107897e34350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R05756b8307cd404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rb40228f8cef84f32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Infant solitary, social and mother–infant play time</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Results Text: Infant gorilla play-category proportions</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — use only if Kerney lacks required observations
@@ -350,13 +350,13 @@
         <x:v>Francesca Hicks dissertation: Table 1 note, Behavioural Data and References (local final draft). Kerney Online Resources 1–2: exact overlap still unresolved.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 28 / printed p. 22, Results, Play Behavior. Solitary, social and mother–infant proportions use total observed PLAY time as denominator, not the full activity budget. Tables 3–9 provide statistical comparisons; Table 1 identifies individuals. Resolve Kerney coverage and denominators before extraction.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/2442186170/Play Behavior in Infant Western Lowland Gorill.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +508,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Mallavarapu, S. (2001). Play behavior in infant western lowland gorillas (Gorilla gorilla gorilla) at the Lincoln Park Zoo. Honors thesis, Southern Illinois University Carbondale. https://opensiuc.lib.siu.edu/uhp_theses/147/</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Results Text</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Repository thesis (not downloaded)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Fran: explicitly named data source. Planned folder: Mallavarapu__2001. Target: Source tables / results to select. Honours thesis, not journal article. Retain infant ages, individual and play-category distinctions. Verify species-average derivation and overlap with other play compilations. Repository URL is a source link; DOI/alternate identifier remains unassigned.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 28 / printed p. 22, Results, Play Behavior. Solitary, social and mother–infant proportions use total observed PLAY time as denominator, not the full activity budget. Tables 3–9 provide statistical comparisons; Table 1 identifies individuals. Resolve Kerney coverage and denominators before extraction. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/2442186170/Play Behavior in Infant Western Lowland Gorill.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — use only if Kerney lacks required observations</x:v>
@@ -550,7 +552,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Infant solitary, social and mother–infant play time</x:v>
+        <x:v>Infant gorilla play-category proportions</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -695,7 +697,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="100" customHeight="1">
@@ -703,7 +705,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -987,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74AD4BD4-59C6-49FE-97BA-1507781E8B9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD608FEE-B45B-449A-8D9F-7243B8B186AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2449B202-734B-4246-9A57-AAE747B9F5AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6EFEF4A-2550-473B-AFB8-3A2B37DA1060}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98BC9BB3-1327-41FB-93D7-9BA6DB8BE004}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C0101B-4FD6-4F6A-89C9-68AD3571D542}"/>
 </file>